--- a/results.xlsx
+++ b/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\VScode\RouteCreator\AlgorithmCompare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E3454B-B16B-41DE-9E92-6157B2925E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CFCFCF5-3601-4148-8091-CB525AD54F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ga_experiments" sheetId="2" r:id="rId1"/>
@@ -665,7 +665,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -714,6 +714,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -743,48 +749,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -794,6 +787,20 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1416,6 +1423,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="385463248"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -2053,6 +2061,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="467465456"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -3697,203 +3706,203 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2">
         <v>75</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>9</v>
       </c>
       <c r="E2">
         <v>15</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3">
         <v>80</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>14</v>
       </c>
       <c r="E3">
         <v>16</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>17</v>
       </c>
       <c r="B4">
         <v>80</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>19</v>
       </c>
       <c r="E4">
         <v>16</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>22</v>
       </c>
       <c r="B5">
         <v>80</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>24</v>
       </c>
       <c r="E5">
         <v>16</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>28</v>
       </c>
       <c r="B7">
         <v>35</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>30</v>
       </c>
       <c r="E7">
         <v>10</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>33</v>
       </c>
       <c r="B8">
         <v>29</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>35</v>
       </c>
       <c r="E8">
         <v>9</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>38</v>
       </c>
       <c r="B9">
         <v>32</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>40</v>
       </c>
       <c r="E9">
         <v>8</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" t="s">
         <v>41</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>43</v>
       </c>
       <c r="B10">
         <v>36</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>45</v>
       </c>
       <c r="E10">
         <v>8</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" t="s">
         <v>47</v>
       </c>
     </row>
@@ -3941,742 +3950,742 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>49</v>
       </c>
       <c r="E2">
         <v>2</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3">
         <v>76</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>49</v>
       </c>
       <c r="E3">
         <v>15</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>53</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4">
         <v>75</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>49</v>
       </c>
       <c r="E4">
         <v>15</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>56</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5">
         <v>50</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>49</v>
       </c>
       <c r="E5">
         <v>10</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>59</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7">
         <v>5</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>61</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>62</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" t="s">
         <v>63</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>12</v>
       </c>
       <c r="B8">
         <v>76</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>65</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>62</v>
       </c>
       <c r="E8">
         <v>15</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>12</v>
       </c>
       <c r="B9">
         <v>66</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>62</v>
       </c>
       <c r="E9">
         <v>13</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" t="s">
         <v>69</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>12</v>
       </c>
       <c r="B10">
         <v>71</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>62</v>
       </c>
       <c r="E10">
         <v>14</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" t="s">
         <v>72</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>17</v>
       </c>
       <c r="B12">
         <v>5</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>74</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s">
         <v>75</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" t="s">
         <v>76</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>17</v>
       </c>
       <c r="B13">
         <v>76</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s">
         <v>75</v>
       </c>
       <c r="E13">
         <v>15</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" t="s">
         <v>79</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14">
         <v>75</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" t="s">
         <v>75</v>
       </c>
       <c r="E14">
         <v>15</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" t="s">
         <v>82</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" t="s">
         <v>27</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>22</v>
       </c>
       <c r="B16">
         <v>10</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" t="s">
         <v>85</v>
       </c>
       <c r="E16">
         <v>2</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" t="s">
         <v>86</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>22</v>
       </c>
       <c r="B17">
         <v>76</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" t="s">
         <v>88</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" t="s">
         <v>85</v>
       </c>
       <c r="E17">
         <v>15</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" t="s">
         <v>89</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>22</v>
       </c>
       <c r="B18">
         <v>70</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" t="s">
         <v>91</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" t="s">
         <v>85</v>
       </c>
       <c r="E18">
         <v>14</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" t="s">
         <v>92</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" t="s">
         <v>27</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>28</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" t="s">
         <v>95</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" t="s">
         <v>96</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>28</v>
       </c>
       <c r="B21">
         <v>59</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" t="s">
         <v>98</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" t="s">
         <v>95</v>
       </c>
       <c r="E21">
         <v>15</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" t="s">
         <v>99</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>28</v>
       </c>
       <c r="B22">
         <v>54</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" t="s">
         <v>101</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" t="s">
         <v>95</v>
       </c>
       <c r="E22">
         <v>14</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" t="s">
         <v>102</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>28</v>
       </c>
       <c r="B23">
         <v>43</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" t="s">
         <v>104</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" t="s">
         <v>95</v>
       </c>
       <c r="E23">
         <v>11</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" t="s">
         <v>105</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" t="s">
         <v>27</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" t="s">
         <v>27</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>33</v>
       </c>
       <c r="B25">
         <v>0</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" t="s">
         <v>107</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" t="s">
         <v>108</v>
       </c>
       <c r="E25">
         <v>2</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" t="s">
         <v>109</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>33</v>
       </c>
       <c r="B26">
         <v>63</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" t="s">
         <v>111</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" t="s">
         <v>108</v>
       </c>
       <c r="E26">
         <v>15</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" t="s">
         <v>112</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>33</v>
       </c>
       <c r="B27">
         <v>55</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" t="s">
         <v>114</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" t="s">
         <v>108</v>
       </c>
       <c r="E27">
         <v>15</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" t="s">
         <v>115</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" t="s">
         <v>27</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" t="s">
         <v>27</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>38</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" t="s">
         <v>117</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" t="s">
         <v>118</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" t="s">
         <v>119</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>38</v>
       </c>
       <c r="B30">
         <v>68</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" t="s">
         <v>121</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" t="s">
         <v>118</v>
       </c>
       <c r="E30">
         <v>15</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" t="s">
         <v>122</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>38</v>
       </c>
       <c r="B31">
         <v>52</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" t="s">
         <v>124</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" t="s">
         <v>118</v>
       </c>
       <c r="E31">
         <v>15</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" t="s">
         <v>125</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" t="s">
         <v>27</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" t="s">
         <v>27</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>43</v>
       </c>
       <c r="B33">
         <v>5</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" t="s">
         <v>127</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" t="s">
         <v>128</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" t="s">
         <v>129</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>43</v>
       </c>
       <c r="B34">
         <v>60</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" t="s">
         <v>131</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" t="s">
         <v>128</v>
       </c>
       <c r="E34">
         <v>15</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" t="s">
         <v>132</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>43</v>
       </c>
       <c r="B35">
         <v>50</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" t="s">
         <v>134</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" t="s">
         <v>128</v>
       </c>
       <c r="E35">
         <v>13</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" t="s">
         <v>135</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" t="s">
         <v>136</v>
       </c>
     </row>
@@ -4727,203 +4736,203 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2">
         <v>75</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>138</v>
       </c>
       <c r="E2">
         <v>15</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>139</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3">
         <v>46</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>141</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>142</v>
       </c>
       <c r="E3">
         <v>9</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>143</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>17</v>
       </c>
       <c r="B4">
         <v>60</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>145</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>146</v>
       </c>
       <c r="E4">
         <v>12</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>147</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>22</v>
       </c>
       <c r="B5">
         <v>80</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>149</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>150</v>
       </c>
       <c r="E5">
         <v>16</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>151</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>28</v>
       </c>
       <c r="B7">
         <v>16</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>153</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>154</v>
       </c>
       <c r="E7">
         <v>4</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" t="s">
         <v>155</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>33</v>
       </c>
       <c r="B8">
         <v>16</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>157</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>158</v>
       </c>
       <c r="E8">
         <v>4</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" t="s">
         <v>159</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>38</v>
       </c>
       <c r="B9">
         <v>7</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>161</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>162</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" t="s">
         <v>163</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>43</v>
       </c>
       <c r="B10">
         <v>16</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>165</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>166</v>
       </c>
       <c r="E10">
         <v>4</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" t="s">
         <v>167</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" t="s">
         <v>168</v>
       </c>
     </row>
@@ -4955,783 +4964,771 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="G1" s="9" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="G1" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="M1" s="9" t="s">
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="M1" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
     </row>
     <row r="2" spans="1:17" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="K2" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="N2" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="P2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="11" t="s">
+      <c r="Q2" s="5" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="7">
         <v>75</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="7">
         <v>15</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="7">
         <v>10</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="K3" s="13">
+      <c r="K3" s="7">
         <v>2</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="M3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="13">
+      <c r="N3" s="7">
         <v>75</v>
       </c>
-      <c r="O3" s="12" t="s">
+      <c r="O3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="P3" s="12" t="s">
+      <c r="P3" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="Q3" s="13">
+      <c r="Q3" s="7">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="10">
         <v>80</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="10">
         <v>16</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="8">
         <v>76</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="15">
+      <c r="K4" s="8">
         <v>15</v>
       </c>
-      <c r="M4" s="14" t="s">
+      <c r="M4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N4" s="15">
+      <c r="N4" s="8">
         <v>46</v>
       </c>
-      <c r="O4" s="14" t="s">
+      <c r="O4" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="P4" s="14" t="s">
+      <c r="P4" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="Q4" s="15">
+      <c r="Q4" s="8">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="7">
         <v>80</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="7">
         <v>16</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="7">
         <v>75</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="7">
         <v>15</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="M5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="N5" s="13">
+      <c r="N5" s="7">
         <v>60</v>
       </c>
-      <c r="O5" s="12" t="s">
+      <c r="O5" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="P5" s="12" t="s">
+      <c r="P5" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="Q5" s="7">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="8">
         <v>80</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="8">
         <v>16</v>
       </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="8">
         <v>50</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="K6" s="15">
+      <c r="K6" s="8">
         <v>10</v>
       </c>
-      <c r="M6" s="16" t="s">
+      <c r="M6" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="N6" s="17">
+      <c r="N6" s="10">
         <v>80</v>
       </c>
-      <c r="O6" s="16" t="s">
+      <c r="O6" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="P6" s="16" t="s">
+      <c r="P6" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="Q6" s="17">
+      <c r="Q6" s="10">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="8">
         <v>35</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="8">
         <v>10</v>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="8">
         <v>5</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="J7" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="K7" s="15">
+      <c r="K7" s="8">
         <v>2</v>
       </c>
-      <c r="M7" s="14" t="s">
+      <c r="M7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N7" s="15">
+      <c r="N7" s="8">
         <v>16</v>
       </c>
-      <c r="O7" s="14" t="s">
+      <c r="O7" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="P7" s="14" t="s">
+      <c r="P7" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="Q7" s="15">
+      <c r="Q7" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="7">
         <v>29</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="7">
         <v>9</v>
       </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="13">
         <v>76</v>
       </c>
-      <c r="I8" s="19" t="s">
+      <c r="I8" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="J8" s="19" t="s">
+      <c r="J8" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="K8" s="20">
+      <c r="K8" s="13">
         <v>15</v>
       </c>
-      <c r="M8" s="12" t="s">
+      <c r="M8" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="N8" s="13">
+      <c r="N8" s="7">
         <v>16</v>
       </c>
-      <c r="O8" s="12" t="s">
+      <c r="O8" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="P8" s="12" t="s">
+      <c r="P8" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="Q8" s="13">
+      <c r="Q8" s="7">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="8">
         <v>32</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="8">
         <v>8</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="8">
         <v>66</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="J9" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="K9" s="15">
+      <c r="K9" s="8">
         <v>13</v>
       </c>
-      <c r="M9" s="14" t="s">
+      <c r="M9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N9" s="15">
+      <c r="N9" s="8">
         <v>7</v>
       </c>
-      <c r="O9" s="14" t="s">
+      <c r="O9" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="P9" s="14" t="s">
+      <c r="P9" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="Q9" s="15">
+      <c r="Q9" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="7">
         <v>36</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="7">
         <v>8</v>
       </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="7">
         <v>71</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="J10" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="K10" s="13">
+      <c r="K10" s="7">
         <v>14</v>
       </c>
-      <c r="M10" s="12" t="s">
+      <c r="M10" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="N10" s="13">
+      <c r="N10" s="7">
         <v>16</v>
       </c>
-      <c r="O10" s="12" t="s">
+      <c r="O10" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="P10" s="12" t="s">
+      <c r="P10" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="Q10" s="13">
+      <c r="Q10" s="7">
         <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="F11" s="2"/>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="7">
         <v>5</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J11" s="12" t="s">
+      <c r="J11" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K11" s="13">
+      <c r="K11" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="F12" s="2"/>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="15">
+      <c r="H12" s="8">
         <v>76</v>
       </c>
-      <c r="I12" s="14" t="s">
+      <c r="I12" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="J12" s="14" t="s">
+      <c r="J12" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K12" s="15">
+      <c r="K12" s="8">
         <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="F13" s="2"/>
-      <c r="G13" s="12" t="s">
+      <c r="G13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="7">
         <v>75</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="I13" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="J13" s="12" t="s">
+      <c r="J13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K13" s="13">
+      <c r="K13" s="7">
         <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="F14" s="2"/>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="7">
         <v>10</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="J14" s="12" t="s">
+      <c r="J14" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="K14" s="13">
+      <c r="K14" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="F15" s="2"/>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H15" s="15">
+      <c r="H15" s="8">
         <v>76</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="I15" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="J15" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="K15" s="15">
+      <c r="K15" s="8">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="7">
         <v>70</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="I16" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="J16" s="12" t="s">
+      <c r="J16" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="K16" s="13">
+      <c r="K16" s="7">
         <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G17" s="19" t="s">
+      <c r="G17" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H17" s="20">
+      <c r="H17" s="13">
         <v>2</v>
       </c>
-      <c r="I17" s="19" t="s">
+      <c r="I17" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="J17" s="19" t="s">
+      <c r="J17" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="K17" s="20">
+      <c r="K17" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G18" s="14" t="s">
+      <c r="G18" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H18" s="15">
+      <c r="H18" s="8">
         <v>59</v>
       </c>
-      <c r="I18" s="14" t="s">
+      <c r="I18" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J18" s="14" t="s">
+      <c r="J18" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="K18" s="15">
+      <c r="K18" s="8">
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G19" s="12" t="s">
+      <c r="G19" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H19" s="13">
+      <c r="H19" s="7">
         <v>54</v>
       </c>
-      <c r="I19" s="12" t="s">
+      <c r="I19" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="J19" s="12" t="s">
+      <c r="J19" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="K19" s="13">
+      <c r="K19" s="7">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G20" s="14" t="s">
+      <c r="G20" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H20" s="15">
+      <c r="H20" s="8">
         <v>43</v>
       </c>
-      <c r="I20" s="14" t="s">
+      <c r="I20" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="J20" s="14" t="s">
+      <c r="J20" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="K20" s="15">
+      <c r="K20" s="8">
         <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G21" s="14" t="s">
+      <c r="G21" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H21" s="15">
+      <c r="H21" s="8">
         <v>0</v>
       </c>
-      <c r="I21" s="14" t="s">
+      <c r="I21" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="J21" s="14" t="s">
+      <c r="J21" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="K21" s="15">
+      <c r="K21" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G22" s="12" t="s">
+      <c r="G22" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="13">
+      <c r="H22" s="7">
         <v>63</v>
       </c>
-      <c r="I22" s="12" t="s">
+      <c r="I22" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="J22" s="12" t="s">
+      <c r="J22" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="K22" s="13">
+      <c r="K22" s="7">
         <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G23" s="14" t="s">
+      <c r="G23" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="15">
+      <c r="H23" s="8">
         <v>55</v>
       </c>
-      <c r="I23" s="14" t="s">
+      <c r="I23" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="J23" s="14" t="s">
+      <c r="J23" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="K23" s="15">
+      <c r="K23" s="8">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G24" s="14" t="s">
+      <c r="G24" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H24" s="15">
+      <c r="H24" s="8">
         <v>1</v>
       </c>
-      <c r="I24" s="14" t="s">
+      <c r="I24" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="J24" s="14" t="s">
+      <c r="J24" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="K24" s="15">
+      <c r="K24" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G25" s="12" t="s">
+      <c r="G25" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H25" s="13">
+      <c r="H25" s="7">
         <v>68</v>
       </c>
-      <c r="I25" s="12" t="s">
+      <c r="I25" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="J25" s="12" t="s">
+      <c r="J25" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="K25" s="13">
+      <c r="K25" s="7">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G26" s="14" t="s">
+      <c r="G26" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H26" s="15">
+      <c r="H26" s="8">
         <v>52</v>
       </c>
-      <c r="I26" s="14" t="s">
+      <c r="I26" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="J26" s="14" t="s">
+      <c r="J26" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="K26" s="15">
+      <c r="K26" s="8">
         <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G27" s="14" t="s">
+      <c r="G27" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H27" s="15">
+      <c r="H27" s="8">
         <v>5</v>
       </c>
-      <c r="I27" s="14" t="s">
+      <c r="I27" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="J27" s="14" t="s">
+      <c r="J27" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="K27" s="15">
+      <c r="K27" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G28" s="12" t="s">
+      <c r="G28" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H28" s="13">
+      <c r="H28" s="7">
         <v>60</v>
       </c>
-      <c r="I28" s="12" t="s">
+      <c r="I28" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="J28" s="12" t="s">
+      <c r="J28" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="K28" s="13">
+      <c r="K28" s="7">
         <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G29" s="14" t="s">
+      <c r="G29" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H29" s="15">
+      <c r="H29" s="8">
         <v>50</v>
       </c>
-      <c r="I29" s="14" t="s">
+      <c r="I29" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="J29" s="14" t="s">
+      <c r="J29" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="K29" s="15">
+      <c r="K29" s="8">
         <v>13</v>
       </c>
     </row>
@@ -5754,106 +5751,106 @@
       <c r="K31" s="23"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
+      <c r="A32" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B32" s="18">
+      <c r="B32" s="11">
         <v>80</v>
       </c>
-      <c r="D32" s="21" t="s">
+      <c r="D32" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E32" s="22">
+      <c r="E32" s="14">
         <v>76</v>
       </c>
-      <c r="G32" s="7" t="s">
+      <c r="G32" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="H32" s="8">
+      <c r="H32" s="3">
         <v>2</v>
       </c>
-      <c r="J32" s="21" t="s">
+      <c r="J32" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="K32" s="18">
+      <c r="K32" s="11">
         <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B33" s="3">
         <v>25.4757852554321</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E33" s="8">
+      <c r="E33" s="3">
         <v>24.0158176422119</v>
       </c>
-      <c r="G33" s="7" t="s">
+      <c r="G33" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="H33" s="8">
+      <c r="H33" s="3">
         <v>25.401726245880099</v>
       </c>
-      <c r="J33" s="7" t="s">
+      <c r="J33" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="K33" s="8">
+      <c r="K33" s="3">
         <v>19.8601248264312</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34" s="3">
         <v>15614.9010978191</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E34" s="8">
+      <c r="E34" s="3">
         <v>32577.5792823107</v>
       </c>
-      <c r="G34" s="21" t="s">
+      <c r="G34" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H34" s="18">
+      <c r="H34" s="11">
         <v>1255.6483439250601</v>
       </c>
-      <c r="J34" s="7" t="s">
+      <c r="J34" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K34" s="8">
+      <c r="K34" s="3">
         <v>23336.176759817801</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B35" s="3">
         <v>16</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="E35" s="8">
+      <c r="E35" s="3">
         <v>15</v>
       </c>
-      <c r="G35" s="7" t="s">
+      <c r="G35" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="H35" s="8">
+      <c r="H35" s="3">
         <v>2</v>
       </c>
-      <c r="J35" s="7" t="s">
+      <c r="J35" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="K35" s="8">
+      <c r="K35" s="3">
         <v>16</v>
       </c>
     </row>
@@ -5881,217 +5878,217 @@
     <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" customWidth="1"/>
+    <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" customWidth="1"/>
     <col min="10" max="10" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="D1" s="23" t="s">
+      <c r="B1" s="21"/>
+      <c r="D1" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="E1" s="23"/>
-      <c r="G1" s="23" t="s">
+      <c r="E1" s="21"/>
+      <c r="G1" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="H1" s="23"/>
-      <c r="J1" s="23" t="s">
+      <c r="H1" s="21"/>
+      <c r="J1" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="K1" s="23"/>
+      <c r="K1" s="21"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="B2" s="18">
+      <c r="B2" s="19">
         <v>80</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="E2" s="22">
+      <c r="E2" s="20">
         <v>76</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="3">
         <v>2</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="K2" s="18">
+      <c r="K2" s="19">
         <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="3">
         <v>25.4757852554321</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="3">
         <v>24.0158176422119</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="3">
         <v>25.401726245880099</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="K3" s="8">
+      <c r="K3" s="3">
         <v>19.8601248264312</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="3">
         <v>15614.9010978191</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="3">
         <v>32577.5792823107</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="H4" s="18">
+      <c r="H4" s="19">
         <v>1255.6483439250601</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K4" s="3">
         <v>23336.176759817801</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="3">
         <v>16</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="3">
         <v>15</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="3">
         <v>2</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="3">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="17" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="15">
         <v>80</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="16">
         <v>25.4757852554321</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="16">
         <v>15614.9010978191</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="15">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="15">
         <v>76</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="16">
         <v>24.0158176422119</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="16">
         <v>32577.5792823107</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="15">
         <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="15">
         <v>2</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="16">
         <v>25.401726245880099</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="16">
         <v>1255.6483439250601</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B14" s="24">
+      <c r="B14" s="15">
         <v>80</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="16">
         <v>19.8601248264312</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="16">
         <v>23336.176759817801</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="15">
         <v>16</v>
       </c>
     </row>

--- a/results.xlsx
+++ b/results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\VScode\RouteCreator\AlgorithmCompare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CFCFCF5-3601-4148-8091-CB525AD54F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{045DAC0E-1185-4A41-A851-44AEE2ED1D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ga_experiments" sheetId="2" r:id="rId1"/>
@@ -621,10 +621,10 @@
     <t>Время, с.</t>
   </si>
   <si>
-    <t>Интерес, ед.</t>
-  </si>
-  <si>
     <t>Алгоритм</t>
+  </si>
+  <si>
+    <t>Фитнес-функция, ед.</t>
   </si>
 </sst>
 </file>
@@ -901,15 +901,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="ru-RU"/>
-              <a:t>Полученный</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ru-RU" baseline="0"/>
-              <a:t> и</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ru-RU"/>
-              <a:t>нтерес и время работы</a:t>
+              <a:t>Фитнес-функция и время работы</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -958,7 +950,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Интерес, ед.</c:v>
+                  <c:v>Фитнес-функция, ед.</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1245,7 +1237,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="ru-RU"/>
-                  <a:t>Интерес, ед.</a:t>
+                  <a:t>Фитнес-функция, ед.</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -1547,7 +1539,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="ru-RU"/>
-              <a:t>Полученный интерес и дистанция</a:t>
+              <a:t>Фитнес-функция и дистанция</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1596,7 +1588,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Интерес, ед.</c:v>
+                  <c:v>Фитнес-функция, ед.</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1882,8 +1874,19 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="ru-RU" sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Фитнес-функция</a:t>
+                </a:r>
+                <a:r>
                   <a:rPr lang="ru-RU"/>
-                  <a:t>Интерес, ед.</a:t>
+                  <a:t>, ед.</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -6007,12 +6010,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="B10" s="17" t="s">
         <v>187</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>186</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>185</v>
